--- a/src/attributions/attributions_ig_traj_396.xlsx
+++ b/src/attributions/attributions_ig_traj_396.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG16"/>
+  <dimension ref="A1:GG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2140,52 +2140,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06994985911365439</v>
+        <v>0.1468833533053141</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01316139550653413</v>
+        <v>-0.01716673244619608</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05709290230851371</v>
+        <v>-0.1178965431089652</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03421400537711818</v>
+        <v>0.1871642052964572</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01326639404992944</v>
+        <v>-0.02530287532997286</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05982326027720154</v>
+        <v>-0.09917447753011109</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00086953419661511</v>
+        <v>-0.007097786545542426</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,40 +2203,40 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-9.715730160522831e-12</v>
+        <v>-9.766524754997026e-11</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0013145632157747</v>
+        <v>0.006210199181058357</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01824886387265805</v>
+        <v>-0.06157026222348962</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02193328436901761</v>
+        <v>-0.08882696601433628</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.001868225734852499</v>
+        <v>-0.08409584662216901</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.008301576578952063</v>
+        <v>0.02145561136553456</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,25 +2257,25 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01915996438687695</v>
+        <v>-0.03337481531071075</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.0150934466451308</v>
+        <v>-0.04847278811671655</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.07897179356482356</v>
+        <v>0.3925053090913105</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,79 +2284,79 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.02010247893424449</v>
+        <v>-0.04836492724815908</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.06230868306749018</v>
+        <v>-0.05680137879179694</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01453397261410901</v>
+        <v>-0.009519289320065851</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01529800562673683</v>
+        <v>-0.04556557773725211</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.008025308917821354</v>
+        <v>-0.02239015190129566</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03640351990302985</v>
+        <v>0.06124536581212148</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002623953784580899</v>
+        <v>0.1006562939533937</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01323925937495189</v>
+        <v>0.1018276620679153</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0415958098687407</v>
+        <v>0.1727510479464165</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,187 +2365,187 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01931342315821017</v>
+        <v>-0.08957290889797855</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01257813956426802</v>
+        <v>-0.1426823321545233</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.0176707530007723</v>
+        <v>-0.06291996624957769</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.003237043775878434</v>
+        <v>-0.006255659895255133</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03700517857712976</v>
+        <v>0.09415380543562707</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.007420924786886975</v>
+        <v>-0.1748012391696648</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01330170377393975</v>
+        <v>0.1031597713340841</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.00660979783172048</v>
+        <v>0.07364477433113323</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01221519136561024</v>
+        <v>-0.06753015732871656</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.005879397387804511</v>
+        <v>-0.02174575301836593</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03673798630459103</v>
+        <v>0.08593092883866514</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01280780490158825</v>
+        <v>-0.00048368799819619</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.004564017310019292</v>
+        <v>-0.08386026978673557</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05275052856657349</v>
+        <v>0.001721002775582066</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01060444266146091</v>
+        <v>-0.03457788064960824</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0110236688766341</v>
+        <v>0.06062091678228722</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.009567298470519868</v>
+        <v>0.1290823298265821</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.007346226316821109</v>
+        <v>-0.008390218754030607</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.00702143873724737</v>
+        <v>-0.003042641113449865</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.03282145735220546</v>
+        <v>-0.08161911483563372</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.003548155704533139</v>
+        <v>-0.06926920293828488</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,52 +2554,52 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.00202696269231275</v>
+        <v>-0.06775004559219758</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01547682061642366</v>
+        <v>0.0429069664519415</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.003550734616464563</v>
+        <v>0.02430001644626483</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01085202368263255</v>
+        <v>-0.06974945524278056</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03747831357210858</v>
+        <v>0.07233445365997004</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01284605707696785</v>
+        <v>-0.07586886595711174</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,37 +2608,37 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.003955205447739193</v>
+        <v>-0.03389266895192474</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03349674975986979</v>
+        <v>0.07555515187101028</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01271468672936882</v>
+        <v>-0.1171269257800774</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01595905813655106</v>
+        <v>0.01450167474669479</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.007023377235511733</v>
+        <v>-0.04115136268048374</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001520185828778451</v>
+        <v>0.06504819542249472</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.006565446093303434</v>
+        <v>0.02046403888792517</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03984951544639709</v>
+        <v>0.07587257779103967</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,57 +2674,57 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01997284887404845</v>
+        <v>-0.006000054185842735</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.008089423562037257</v>
+        <v>0.05375130192842303</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.217827529562806</v>
+        <v>0.2532218593528002</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1462272256707496</v>
+        <v>-0.2018138214145931</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1007373398116755</v>
+        <v>-0.03333138224236641</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2733,19 +2733,19 @@
         <v>-0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1200035417341696</v>
+        <v>0.1933456526677653</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09446681042569798</v>
+        <v>-0.1868831738766666</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1058266701631268</v>
+        <v>-0.05996199944282245</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009021080763612114</v>
+        <v>0.01423560392847332</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.009803003775371435</v>
+        <v>-0.01548216950995094</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0005739947957383369</v>
+        <v>-0.0005111332811644447</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
@@ -2781,52 +2781,52 @@
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.048521942815441</v>
+        <v>-0.01453930089008748</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02910202746031874</v>
+        <v>-0.1189184740218282</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1067635787636451</v>
+        <v>-0.03169085674614137</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.02161106720596098</v>
+        <v>0.1024356804376414</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04437283952284311</v>
+        <v>-0.04538069965512331</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.1124254770320274</v>
+        <v>0.06274746185099951</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,31 +2835,31 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3692869523994848</v>
+        <v>0.2722569831331343</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03185798774822611</v>
+        <v>-0.1732092192925213</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1233270859799434</v>
+        <v>-0.2269578438230116</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,19 +2868,19 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.007065600229175921</v>
+        <v>0.009413238470176166</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1632950662359478</v>
+        <v>-0.0416101918088435</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.0521721598719531</v>
+        <v>-0.008836269463386963</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1837114996722033</v>
+        <v>0.01331730029690869</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.03039242697876449</v>
+        <v>0.06999342088490119</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2090224988283516</v>
+        <v>0.08024991585713766</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,97 +2925,97 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2181192725783027</v>
+        <v>0.2098686141333214</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0007868063141094659</v>
+        <v>-0.009454441710888656</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01259325845116288</v>
+        <v>-0.04648268633231181</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05950032794030061</v>
+        <v>-0.1241837326870655</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02614376529994064</v>
+        <v>0.1170432739320873</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01075612939155658</v>
+        <v>0.004055952994783086</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.05632596364425869</v>
+        <v>-0.117344378222771</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06724754931439728</v>
+        <v>0.1338178678154169</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1692441117615368</v>
+        <v>0.1133768084016513</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.04096096769241803</v>
+        <v>-0.1336696378804358</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0406938438179704</v>
+        <v>0.1280832318653802</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.03970439220185531</v>
+        <v>0.01764628303528247</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002886593413639251</v>
+        <v>-0.006685874085285502</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.04100202871695391</v>
+        <v>0.04161798095114829</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.004296795394260962</v>
+        <v>-0.05950507544951891</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
@@ -3060,124 +3060,124 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.090001988922972</v>
+        <v>-0.1005952276450929</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02014051466517268</v>
+        <v>0.0314958333266616</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.01658017971226415</v>
+        <v>-0.05602254235895137</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.03306160236397859</v>
+        <v>0.0331159755725175</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.06055508300288623</v>
+        <v>0.08609299688100581</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02381218296399218</v>
+        <v>0.03058391912182956</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03914193919808775</v>
+        <v>-0.09079717977198828</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.05014801466279573</v>
+        <v>0.1094903208923319</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.1003504364985555</v>
+        <v>0.04382424443231323</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.05057113420650077</v>
+        <v>-0.04749157993286993</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.03170397656632804</v>
+        <v>0.06284519199218191</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.008537760975077819</v>
+        <v>-0.006413862933124878</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.04600497217929938</v>
+        <v>-0.1530452611855802</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.04657349276722474</v>
+        <v>0.1464241738498634</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.04315124479140321</v>
+        <v>0.006298580352829371</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
@@ -3186,58 +3186,58 @@
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.07696754350678763</v>
+        <v>-0.09132032152572421</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0739689946995217</v>
+        <v>-0.07820791270320927</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.02648865566944717</v>
+        <v>0.0550817923054805</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.07475289727738188</v>
+        <v>0.07318869482619542</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03787519527507545</v>
+        <v>0.1569776942429307</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.08728981310799777</v>
+        <v>-0.07856483868499178</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03150645121652419</v>
+        <v>-0.08530782868937228</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.02414960623463452</v>
+        <v>0.07923364391592169</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02456641208183855</v>
+        <v>0.03446282332550096</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01468036649522814</v>
+        <v>0.01943128399138893</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.007698709718938207</v>
+        <v>-0.01353897616074683</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006791962101931512</v>
+        <v>0.05242660988418642</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01915687146732925</v>
+        <v>0.01110214304332986</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01078886493280247</v>
+        <v>-0.01368467266441365</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001647799861715627</v>
+        <v>-0.0005695022697151011</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.00025190637917091</v>
+        <v>-0.005615640547698726</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001667961972359667</v>
+        <v>7.20092527727744e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01928449481757365</v>
+        <v>-0.01367919986290485</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0230584053843786</v>
+        <v>-0.05294158895335584</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002495240783553944</v>
+        <v>-0.0123796170153349</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002764602595353769</v>
+        <v>0.01019195633419059</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,52 +3395,52 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01755303853754191</v>
+        <v>-0.01186347293563644</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.005024979670600217</v>
+        <v>-0.02111357123437578</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.04673803066608814</v>
+        <v>0.08558540916967657</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.009006956345056704</v>
+        <v>-0.01646972120154</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.006465964589002495</v>
+        <v>-0.01572768666772076</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.003715231048417724</v>
+        <v>-0.004827997387907724</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01399798199680543</v>
+        <v>-0.007825695338639797</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001520198702781423</v>
+        <v>0.002308382318799643</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03418747982740929</v>
+        <v>0.01768696414131995</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01501940881362629</v>
+        <v>0.04174881666257255</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01198114915951823</v>
+        <v>0.03364583127471926</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01644032500394804</v>
+        <v>0.04099749049120104</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01316908090442288</v>
+        <v>0.001151177175404087</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01821063409955048</v>
+        <v>-0.03714097677550613</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,76 +3521,76 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0007725904297555667</v>
+        <v>-0.01046960406680436</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00104080936452394</v>
+        <v>-0.002349275512795706</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006381491755246992</v>
+        <v>0.02420542335859007</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0008337732471837716</v>
+        <v>-0.03462299210851444</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00129170100230547</v>
+        <v>0.04442982763116885</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01519441862758138</v>
+        <v>0.02746300484914008</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.004227166173976129</v>
+        <v>-0.01360766349006135</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0006517472063143082</v>
+        <v>-0.004175535673159557</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.005921585872880115</v>
+        <v>0.02142093585175857</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.000549863869421545</v>
+        <v>-0.01568676758563036</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0001659195889902868</v>
+        <v>-0.001110470127163424</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0171232900908689</v>
+        <v>-0.003651699085836633</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,25 +3623,25 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.002561774824204767</v>
+        <v>-0.0138544792401314</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01508498496717742</v>
+        <v>-0.001314603514511746</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002563809276230584</v>
+        <v>0.03145498583169162</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3653,10 +3653,10 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01239948043737637</v>
+        <v>-0.01279119173917899</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,94 +3665,94 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.009574658122283851</v>
+        <v>0.002886056744397371</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.003422486569711622</v>
+        <v>0.02458154333342059</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.006690269382926529</v>
+        <v>-0.01081401495017262</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001165373692854197</v>
+        <v>-0.02051569203556368</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003366814866980144</v>
+        <v>0.003563422025805357</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.001094311243342646</v>
+        <v>-9.717980619672815e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01508922729203346</v>
+        <v>-0.002335179058332378</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03470761624459432</v>
+        <v>0.01499446520321281</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.005075754498263352</v>
+        <v>-0.01700788526661338</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.000176137714440469</v>
+        <v>-0.009376188323831152</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009592935695584176</v>
+        <v>0.01580178017323954</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.008330673274877815</v>
+        <v>-0.02077306885543498</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01621642784548195</v>
+        <v>0.0162439781923969</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0206537012142523</v>
+        <v>0.004902595884367472</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.008040891104569004</v>
+        <v>0.01352237324468567</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.002502535268260733</v>
+        <v>0.0003695043094960039</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.004945959271245903</v>
+        <v>-0.03385002077437842</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,13 +3812,13 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02300959617989696</v>
+        <v>0.01079817311355758</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,13 +3830,13 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.004015263705812197</v>
+        <v>0.01698537956827134</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1241300437423404</v>
+        <v>0.05980026827225055</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0193089306755991</v>
+        <v>-0.0284432353524125</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01860889551611414</v>
+        <v>-0.00598856058583258</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05518312534412023</v>
+        <v>0.08128297745988014</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.070730149723348</v>
+        <v>-0.02884117310151697</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02480267153862867</v>
+        <v>-0.005228320950689353</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008968325500849549</v>
+        <v>-0.00434846079620899</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.004807797111578471</v>
+        <v>-0.009973410680871042</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.371692952234027e-05</v>
+        <v>0.000260677666669869</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04103189887180352</v>
+        <v>-0.0146007301076234</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02718509663999042</v>
+        <v>-0.01861616138297268</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01144453165757756</v>
+        <v>-0.0004002842254450772</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03107694069621219</v>
+        <v>0.02381300632716692</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02745193754701533</v>
+        <v>-0.008597081995682716</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01670937105065463</v>
+        <v>-0.005823354460768549</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1929359764811916</v>
+        <v>0.09478846580803842</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07517317125382618</v>
+        <v>-0.01734196516313475</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,94 +4003,94 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0009099615574351315</v>
+        <v>0.01034619146702061</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01350424943969704</v>
+        <v>-0.003852437258943205</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.04616367215943096</v>
+        <v>-0.01519516217558497</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01096067445668646</v>
+        <v>0.005942237384122198</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02261979903386492</v>
+        <v>0.01603983386182907</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0975562504177975</v>
+        <v>0.04291896891534303</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.03294690110003337</v>
+        <v>0.01473807493729601</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1134431476566394</v>
+        <v>0.05659570169040377</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01027277804203492</v>
+        <v>-0.02559382917573149</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01077981817044397</v>
+        <v>-0.01883517079292131</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02820427114775236</v>
+        <v>-0.0250337817608954</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0003988759539411895</v>
+        <v>0.01008188791118073</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.03399854441729087</v>
+        <v>0.01331491468171446</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02542111903532525</v>
+        <v>-0.04820857280397723</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02687471990553795</v>
+        <v>0.007908200034761427</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01113418622771262</v>
+        <v>0.02087455876089555</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02347860777193973</v>
+        <v>-0.02610433058170366</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.00668072831454471</v>
+        <v>0.005617702646817495</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03334149076991951</v>
+        <v>0.01231728842095385</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.08937100020755065</v>
+        <v>-0.01818951454183398</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03525600754625089</v>
+        <v>-0.01248190291445074</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.008066276423123409</v>
+        <v>-0.009122604065681805</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.0007953471731210252</v>
+        <v>-0.02056652442376224</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.007066881272616677</v>
+        <v>0.01155964835495005</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.0006259192218805173</v>
+        <v>-0.03062229582675704</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0009782762551912288</v>
+        <v>0.009014155808795051</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01898523128515474</v>
+        <v>0.007211016946245414</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01056804788960394</v>
+        <v>-0.006911428485513788</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002559690416999884</v>
+        <v>-0.02175234126593022</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03352086517445372</v>
+        <v>0.0008374757269752813</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03639175329087033</v>
+        <v>0.005748261809932584</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04369758961480787</v>
+        <v>-0.003314189772644674</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.005187430784189608</v>
+        <v>0.006859215588648872</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01646818506335573</v>
+        <v>0.007327596365210579</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03602767126200614</v>
+        <v>-0.03020272803500181</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.00741530496074033</v>
+        <v>0.002274653629187258</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01949174005763412</v>
+        <v>0.01307263662430466</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03657766432310335</v>
+        <v>-0.018825765044271</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02407465007401665</v>
+        <v>0.007443444725384826</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01595182858534985</v>
+        <v>0.04556519980683862</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05824554867699334</v>
+        <v>0.01002865017549067</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,10 +4369,10 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01812409540932537</v>
+        <v>-0.01730387371937581</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,16 +4381,16 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.000565249581921097</v>
+        <v>0.002318378998897767</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.04537632800952431</v>
+        <v>-0.0122332372321252</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.04004586932561209</v>
+        <v>0.0002174000537640983</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4112454454087895</v>
+        <v>0.1742139486461227</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2680988961135768</v>
+        <v>-0.1001635383154783</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0639289497606631</v>
+        <v>-0.04690409160516187</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5006,22 +5006,22 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.239660441603601</v>
+        <v>0.1787676685904626</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2488363692615805</v>
+        <v>-0.1554589211784427</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1221988524737534</v>
+        <v>-0.09343959653332001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04630098033682213</v>
+        <v>0.03856217173878157</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01561544308691271</v>
+        <v>-0.01688773152711903</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03762181748389932</v>
+        <v>-0.01520103464623454</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,52 +5066,52 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1555617206428253</v>
+        <v>-0.04260072418003649</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02202931839693563</v>
+        <v>-0.09311697390805575</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03506564185680215</v>
+        <v>-0.1219299615648137</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01659281192984714</v>
+        <v>0.1065290730364113</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03881498546151499</v>
+        <v>-0.05809825057335934</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1239466312865073</v>
+        <v>0.05849038483475855</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,19 +5120,19 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.5101479823448716</v>
+        <v>0.1855012128226176</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.02731528625162876</v>
+        <v>-0.03048476318616476</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1885928567156652</v>
+        <v>-0.2038436530794754</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.009044952109878457</v>
+        <v>-0.03554123775776184</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1050612750458147</v>
+        <v>-0.0190568802038453</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.152401463336659</v>
+        <v>-0.02249645293441932</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2187976074905324</v>
+        <v>0.04199903999590413</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1194362713558662</v>
+        <v>0.03979651521850295</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1337065694987881</v>
+        <v>0.04140923044833601</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2922781090310419</v>
+        <v>0.2131699620591115</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.001713097253712505</v>
+        <v>-0.008959765736075237</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.006804078273705326</v>
+        <v>-0.05820208303508782</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.09677222943851789</v>
+        <v>-0.07086201325137313</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03494569292099962</v>
+        <v>0.08912530115248102</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.0194454954554744</v>
+        <v>0.03081285045280363</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.07988583071648979</v>
+        <v>-0.09035232194751025</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1854163762056791</v>
+        <v>0.242593998647511</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1177705550796443</v>
+        <v>0.1302474710072964</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,49 +5282,49 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.06228161009445948</v>
+        <v>-0.05449803716389157</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.07224666734636233</v>
+        <v>0.09859717298383093</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.00276877684815864</v>
+        <v>0.04304350880688956</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01175496810931885</v>
+        <v>-0.002597078409237464</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.06090145064101328</v>
+        <v>0.01242444015450436</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03510198921394354</v>
+        <v>-0.05162893682675743</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5333,25 +5333,25 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.08228384809237217</v>
+        <v>-0.08118836138062797</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.01827137800352406</v>
+        <v>0.06812458754738208</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02058108888477084</v>
+        <v>0.03498370539595751</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5360,79 +5360,79 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.01384865783479854</v>
+        <v>0.007511760553187761</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.06441397617326104</v>
+        <v>0.00505787441534315</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.007603654790727663</v>
+        <v>-0.04911319766427085</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.01813568614745451</v>
+        <v>0.01032100915597314</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.1024808304655887</v>
+        <v>0.07209473010907039</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.06525378131044665</v>
+        <v>0.04761720864404806</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1108680346951695</v>
+        <v>-0.06261788702706564</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.1008974882619283</v>
+        <v>-0.09226423403017439</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01481128683409949</v>
+        <v>-0.008058769289261376</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,97 +5444,97 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.07161762720417426</v>
+        <v>-0.07290025571601379</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06298052070297494</v>
+        <v>0.1120470606782537</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.006526077038063694</v>
+        <v>0.02716603526165874</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.03219864091886566</v>
+        <v>-0.03429184323362664</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.07855963223506211</v>
+        <v>0.02515195603601677</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.03716087181033577</v>
+        <v>-0.05779928748028183</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
         <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.07608179121404843</v>
+        <v>0.02364159190378178</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.03966518899996726</v>
+        <v>0.07792359093102498</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1307261107569999</v>
+        <v>-0.07110230282649861</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.0358030993279297</v>
+        <v>-0.01841059185224659</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02580522029738367</v>
+        <v>0.03212549708243989</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>-0</v>
@@ -5543,216 +5543,216 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>1.161870703768859</v>
+        <v>0.1117662588378234</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6751129565730145</v>
+        <v>-0.4467358975363916</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1589782179473843</v>
+        <v>-0.3340942412849824</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01700231938271737</v>
+        <v>0.030532693724832</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6427737079531262</v>
+        <v>-0.02819894300841024</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6479858521894282</v>
+        <v>-0.6657914625292556</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3924802003233104</v>
+        <v>-0.5000036310322544</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0001584453343867956</v>
+        <v>0.006298081113549764</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.19940706267688</v>
+        <v>0.1005018693274119</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1482753646922455</v>
+        <v>-0.1348248624429798</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1459640510524763</v>
+        <v>-0.1901378435657317</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03069158246055996</v>
+        <v>0.004854235080054283</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1473907560731351</v>
+        <v>-0.1016160010166999</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08885168973941159</v>
+        <v>0.05354843972518111</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1233605994248155</v>
+        <v>-0.07483999803126905</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01428267223038594</v>
+        <v>0.03161931591074239</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1479902862567761</v>
+        <v>0.2725221780453952</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.1474861947813061</v>
+        <v>-0.07638423141247769</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.128265754078626</v>
+        <v>0.004875037036066873</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.1107123004551502</v>
+        <v>0.02701828136089871</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.310053517337074</v>
+        <v>0.3847642750402528</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.2562555361026237</v>
+        <v>-0.04499798555902784</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2627276706256436</v>
+        <v>-0.506058173245672</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1151356068532475</v>
+        <v>-0.08246794777923559</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0376644226821431</v>
+        <v>-0.158190466694377</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1846972306291376</v>
+        <v>-0.1375328949272227</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.4441266702974772</v>
+        <v>-0.1185146126439145</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.018394202142622</v>
+        <v>-0.03505412528434748</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.457045620868398</v>
+        <v>0.1711503020139422</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2534114300629791</v>
+        <v>0.2626227413741881</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.2236249699701796</v>
+        <v>0.0554527810739823</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
@@ -5761,7 +5761,7 @@
         <v>-0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0.05755961555830785</v>
+        <v>0.01239496156552271</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,43 +5770,43 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.758903122787115</v>
+        <v>0.3257991074148716</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.05422188720591591</v>
+        <v>-0.3136768163222675</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.03009058267169492</v>
+        <v>-0.4128696583184315</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0.1261430274827771</v>
+        <v>-0.1082728930427846</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.2359709720134275</v>
+        <v>0.009246391056199709</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.1088182248609116</v>
+        <v>0.2331566467247071</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.04012190049407723</v>
+        <v>0.1303425054152062</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,7 +5815,7 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.04912927166306812</v>
+        <v>-0.0480774835038856</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -5824,43 +5824,43 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1108196998703627</v>
+        <v>-0.02558318488614329</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.2857761856159745</v>
+        <v>0.2950444432707076</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.07943392102043391</v>
+        <v>0.5044470739291561</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.2146809446727611</v>
+        <v>0.1289813361616374</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1881271301110346</v>
+        <v>0.02934384216368108</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1914999328835408</v>
+        <v>0.2844434672145496</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.06848148473174759</v>
+        <v>0.1568875932471376</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,106 +5869,106 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.0674837722334044</v>
+        <v>-0.0333634009678964</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.1578154803819632</v>
+        <v>-0.02522225201335774</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1155210410244169</v>
+        <v>0.1264283550110777</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.00137227834190234</v>
+        <v>0.03917428439194819</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.009498268649558774</v>
+        <v>-0.07106263226963054</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.2084597716066435</v>
+        <v>-0.0636870503745125</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.000391218766497502</v>
+        <v>0.1083871747854247</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.007987942158085973</v>
+        <v>-0.03307678975233815</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1622142812806846</v>
+        <v>0.1507849741640092</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.08654724539623547</v>
+        <v>-0.004605531895037203</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0295517842257483</v>
+        <v>0.08169352382843564</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.1697067309086501</v>
+        <v>-0.1660343078641666</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.06105702554648922</v>
+        <v>0.1307846071831801</v>
       </c>
       <c r="EE10" t="n">
         <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1095234660939692</v>
+        <v>0.1161768013083736</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.1369749670308411</v>
+        <v>0.1933277620536986</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05322545061811831</v>
+        <v>0.07441878951736323</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0.02502776341358747</v>
+        <v>-0.03668648643022582</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,43 +5986,43 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.2040913345821237</v>
+        <v>-0.04887729752929422</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.2276737965730896</v>
+        <v>0.337581563207448</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.2033475883234453</v>
+        <v>0.04759966149978426</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.2538398152565977</v>
+        <v>-0.06563254142829397</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1856389840318313</v>
+        <v>-0.02379327300127397</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.1685598805832158</v>
+        <v>0.2943338742347804</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.03571488050741511</v>
+        <v>0.1555431348523857</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,25 +6031,25 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.05960983994801395</v>
+        <v>-0.04399918876702714</v>
       </c>
       <c r="FF10" t="n">
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01107277485546167</v>
+        <v>0.05311594691073911</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.07114139126178007</v>
+        <v>-0.1018885231130438</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03293487058352783</v>
+        <v>0.1080509597009059</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,61 +6058,61 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.04353566505574197</v>
+        <v>-0.0705568452870307</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1637622586513561</v>
+        <v>0.01352667672754816</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.05817156186437275</v>
+        <v>-0.02224473431976517</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1356702892824858</v>
+        <v>-0.1712860368874907</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.1202736549756226</v>
+        <v>-0.2329139994740926</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1343331271301771</v>
+        <v>0.02274403937482694</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03393883063404387</v>
+        <v>0.1368858409104142</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.152229765732735</v>
+        <v>-0.1072170432958498</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1924721066360821</v>
+        <v>0.4000176215167411</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1152401362701278</v>
+        <v>0.009212226309224261</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08458070144023767</v>
+        <v>-0.2686522837470932</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1201868796036514</v>
+        <v>0.4931516896817949</v>
       </c>
       <c r="L11" t="n">
         <v>-0</v>
@@ -6159,10 +6159,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1253676682752879</v>
+        <v>-0.09233847849364978</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.09089612842868713</v>
+        <v>-0.2373769338719205</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03814336475982327</v>
+        <v>0.0879889312699612</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01879532451287895</v>
+        <v>-0.09750015508674381</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03485489676743936</v>
+        <v>0.01375739910092633</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04199513458756932</v>
+        <v>-0.03563914831135018</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02619913755114584</v>
+        <v>-0.2417851879879301</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02670816846920809</v>
+        <v>0.05129648277479578</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03298078417140178</v>
+        <v>0.08482367276102616</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02091691539780069</v>
+        <v>-0.05419841903801113</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01534594560943051</v>
+        <v>-0.03757127488758204</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2012277510291645</v>
+        <v>0.5426603979204901</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,79 +6267,79 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.005234173252397055</v>
+        <v>-0.2351766168639169</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.00580964464993633</v>
+        <v>-0.05855377611576622</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04827042508215088</v>
+        <v>-0.05006931905899144</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.09330480961346631</v>
+        <v>-0.02288124216378254</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.0672873519173976</v>
+        <v>-0.1168690340902291</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1151453976621139</v>
+        <v>0.1740587632626067</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.08218872776161752</v>
+        <v>0.1701427424174998</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03438556556862542</v>
+        <v>0.1285334938780363</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1020362536545284</v>
+        <v>0.4061049546383914</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,67 +6348,67 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01024610494974653</v>
+        <v>-0.07343804095511404</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02352178657807901</v>
+        <v>-0.07728336876933159</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03914463477627252</v>
+        <v>-0.143117817507809</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01117821505051086</v>
+        <v>-0.008927171535618905</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02252840654417</v>
+        <v>0.1036498600964846</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0561046915324401</v>
+        <v>-0.2630068431693132</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.05320695580541227</v>
+        <v>0.07634602562137269</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02374181217028895</v>
+        <v>0.01951486551755498</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.0218015111176778</v>
+        <v>-0.1269743390516541</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01303481585824366</v>
+        <v>-0.03085652146153256</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02642628144288648</v>
+        <v>0.1082583857968483</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,46 +6447,46 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.06223031550841257</v>
+        <v>-0.1149119905705799</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01410226948550332</v>
+        <v>-0.1777301131929595</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.002737914156497923</v>
+        <v>-0.01591899258830825</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.05061129978152808</v>
+        <v>-0.09345635439211981</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01440192836623794</v>
+        <v>-0.03549108254710991</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.04406598309598412</v>
+        <v>-0.0368243329122044</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,7 +6501,7 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.002688922498592353</v>
+        <v>0.08063112351940907</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,70 +6510,70 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0505256368629177</v>
+        <v>0.02095383031333507</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.03946649870609888</v>
+        <v>0.06417007931723503</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.00853528477707636</v>
+        <v>0.008676391912133088</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.008883471416870899</v>
+        <v>-0.07654959262627345</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.006733605286018098</v>
+        <v>0.08264058217755887</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01395883829748499</v>
+        <v>-0.002649105356600334</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.00135287373192261</v>
+        <v>-0.1747660268473564</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03941798196443232</v>
+        <v>0.06634815383601009</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,88 +6582,88 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01752258796593774</v>
+        <v>-0.1615036610831479</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01008260125986372</v>
+        <v>-0.05511281599086432</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03299535707745666</v>
+        <v>0.08047460918972182</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02846580465293492</v>
+        <v>-0.1448484924307203</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04572200871993633</v>
+        <v>0.1679035951956798</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02865508733182772</v>
+        <v>0.05067324910718859</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.01021993496347249</v>
+        <v>0.08377186735961371</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.01917984029709819</v>
+        <v>-0.09872286968515348</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01142057861017918</v>
+        <v>-0.008963100782066845</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.06712142606109947</v>
+        <v>-0.07431214221075325</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,13 +6675,13 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02658960102019994</v>
+        <v>0.131987395379984</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>1.062076907914286</v>
+        <v>0.6852494756028162</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9310227340317107</v>
+        <v>-0.6861011841908798</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1077919059022191</v>
+        <v>-0.1558440217950078</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7044532202661427</v>
+        <v>0.603748138340338</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7815384998543998</v>
+        <v>-0.7910310951986897</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2399354910894941</v>
+        <v>-0.3201842590162857</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,49 +6746,49 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2381980265671777</v>
+        <v>0.117550225583785</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1638299827705133</v>
+        <v>-0.1449256685980342</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.03764680715676721</v>
+        <v>-0.2012248665359983</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2078631746849892</v>
+        <v>-0.09631210167722984</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04974190206899036</v>
+        <v>-0.1610732213211121</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02882662712803597</v>
+        <v>-0.1933059558924669</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,25 +6797,25 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1599827710258953</v>
+        <v>0.2569198133341247</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.08445623299074487</v>
+        <v>-0.2189859603591313</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.1261873187948576</v>
+        <v>0.003674793497140894</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6827,16 +6827,16 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8867470450183154</v>
+        <v>0.5222102710875564</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.254734414829416</v>
+        <v>-0.2718130391812776</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1352583370535818</v>
+        <v>-0.4271252316815798</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -6848,22 +6848,22 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1259785647727721</v>
+        <v>0.0362494996124404</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.2800141292668125</v>
+        <v>-0.1070360582638857</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.3872065789422108</v>
+        <v>0.01330352783891416</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,25 +6881,25 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.2180606063576592</v>
+        <v>0.05787001759188001</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.09750149650625174</v>
+        <v>0.1900203783304135</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1533007028457553</v>
+        <v>0.2122154657882626</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
         <v>-0</v>
@@ -6908,22 +6908,22 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4938954433579799</v>
+        <v>0.4760187045103994</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.2223405727526985</v>
+        <v>-0.397479478441833</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07257936543284141</v>
+        <v>-0.2028452395817446</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.2117742107637511</v>
+        <v>-0.2146263054332194</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1330541510699697</v>
+        <v>0.3237997784936956</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.05636835557492208</v>
+        <v>0.05965751781332755</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05636719034686546</v>
+        <v>-0.2429260138356396</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.2270979255699492</v>
+        <v>0.5417427890236228</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07891029873858235</v>
+        <v>0.1817934709900722</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,58 +6983,58 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1726639768648384</v>
+        <v>-0.1878685582111759</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1755805518786877</v>
+        <v>0.3476185439969809</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.04090748278321429</v>
+        <v>0.09580588194268629</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.1221433222923221</v>
+        <v>-0.1738285371979597</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1033182337334861</v>
+        <v>0.06750201258133406</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07098961034583499</v>
+        <v>-0.0928877376059344</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
@@ -7043,19 +7043,19 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06238573808817739</v>
+        <v>-0.1747594673087667</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.1008121497318878</v>
+        <v>0.134475682254452</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.1376494546323105</v>
+        <v>0.01075171993616312</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7070,25 +7070,25 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.04612827210331591</v>
+        <v>9.468266989602761e-05</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.004143161219080902</v>
+        <v>-0.1138512304293956</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01147388149323586</v>
+        <v>-0.02407561171142998</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,49 +7097,49 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09187236175959961</v>
+        <v>-0.1346964951197897</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.1427990795816236</v>
+        <v>0.3098673885983987</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06891253285489464</v>
+        <v>0.1274994074426104</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.1952136634818643</v>
+        <v>-0.1333873097307157</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.1249625363865474</v>
+        <v>0.2766014760039906</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0211288862617114</v>
+        <v>-0.01497668742673648</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,106 +7151,106 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1820717057138982</v>
+        <v>-0.2475419018876383</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.1843020491835352</v>
+        <v>0.3690518941254399</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.03313448966199339</v>
+        <v>0.05425350455880947</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.0520744407835254</v>
+        <v>-0.1262705259538266</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1248745901201601</v>
+        <v>0.1595522778434833</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.002269280659772918</v>
+        <v>0.0004446043685013846</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01877680765330919</v>
+        <v>-0.02313689924090302</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001949719144437032</v>
+        <v>0.2078371329605326</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.06177825145316822</v>
+        <v>0.05987968445474864</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.02136257768987851</v>
+        <v>-0.1568656065178118</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.09107274500506682</v>
+        <v>0.2067239720053075</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5186723122022064</v>
+        <v>0.4908718876989221</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1151118492194106</v>
+        <v>0.05815291174135675</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3972589852137831</v>
+        <v>-0.4193172673463912</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,22 +7285,22 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3861069934730736</v>
+        <v>0.6409911586251532</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.09423712554808331</v>
+        <v>-0.07656546378584714</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.391008057433901</v>
+        <v>-0.4146206671514796</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07540074912470206</v>
+        <v>0.2106806136548068</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.03885256479811341</v>
+        <v>-0.227019648878158</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003245580057836467</v>
+        <v>-0.01984999454924228</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,22 +7342,22 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06798935637340367</v>
+        <v>-0.04245815154400347</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03915472083803847</v>
+        <v>-0.4798464583408518</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03027483531909189</v>
+        <v>-0.2122708688042126</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.07642508534626175</v>
+        <v>0.1465567466517302</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.00502214833889377</v>
+        <v>0.03113797805056141</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.05932754467224097</v>
+        <v>-0.1705448241000739</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.390151193193875</v>
+        <v>0.8749101255484586</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,145 +7405,145 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03064229028918587</v>
+        <v>-0.2303737931235462</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1630309926134079</v>
+        <v>-0.1612483872908721</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1258466534793428</v>
+        <v>-0.1903089402308056</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1231392976191749</v>
+        <v>-0.2475756120249024</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1187523988240726</v>
+        <v>-0.2413581370174335</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1557190632347174</v>
+        <v>0.1101351274821727</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.07732615306520566</v>
+        <v>0.119075495528005</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02346474861806714</v>
+        <v>0.003143564919087123</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2278088342983833</v>
+        <v>0.5322061290200816</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.05923565203936982</v>
+        <v>-0.1397846552232606</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1344275489744019</v>
+        <v>-0.2995977829338917</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1002229734638397</v>
+        <v>-0.1950062841936264</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01140545579097336</v>
+        <v>0.05068986247177513</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08920083533392521</v>
+        <v>0.1702158991091987</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.07010608861945594</v>
+        <v>-0.4515403594532663</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.03864644710731462</v>
+        <v>0.5887209239067918</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01823804189322697</v>
+        <v>0.3919683359213872</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,82 +7555,82 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07775704403633892</v>
+        <v>-0.1783491184193221</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.007994749436489364</v>
+        <v>0.01847381469760883</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.09644038631326031</v>
+        <v>0.1470546919639174</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.06243509931961191</v>
+        <v>-0.00854853240905676</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05278658496295816</v>
+        <v>-0.1890680555833055</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.004551330287982952</v>
+        <v>0.02685823571942652</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.0561831169249196</v>
+        <v>-0.02459262262558854</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03077420112910264</v>
+        <v>-0.01926957002647978</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01083023867872458</v>
+        <v>0.1264690546169137</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,25 +7639,25 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.002806875667316535</v>
+        <v>0.1174284395137866</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.009527285572990013</v>
+        <v>-0.06093034070541392</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01956703911058403</v>
+        <v>0.08486784625931323</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03518963457641573</v>
+        <v>-0.05139568612353233</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01235839753640065</v>
+        <v>-0.06279604012427704</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.09156021504375977</v>
+        <v>0.008917994990613288</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.02554809182724368</v>
+        <v>-0.04091011404337142</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,13 +7702,13 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.02554278675062839</v>
+        <v>-0.06818867845294367</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.08208411782696494</v>
+        <v>0.1491853157311449</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,55 +7717,55 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06717858676039375</v>
+        <v>-0.2145283315169585</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.013275212314281</v>
+        <v>0.0007490470387652337</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.09215256657754509</v>
+        <v>0.1492709547876648</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.07256757285911533</v>
+        <v>-0.2286476348999527</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01621024342507171</v>
+        <v>0.1170569881260012</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.06631725894224907</v>
+        <v>-0.05365814803527066</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,19 +7774,19 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01321131151010192</v>
+        <v>0.08183784132425732</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0298177352584166</v>
+        <v>0.1060424582365105</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01377321515356229</v>
+        <v>-0.04726648727565771</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,25 +7795,25 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02810187476273186</v>
+        <v>-0.07236128796920689</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03792026889440133</v>
+        <v>0.04883709603130627</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,105 +7822,105 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.21064346808799</v>
+        <v>0.6631368412658039</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8634762255456114</v>
+        <v>-0.3314821801856542</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2794060754899577</v>
+        <v>-0.1591292071273836</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7113481146103789</v>
+        <v>0.5870383982821602</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7203171941184746</v>
+        <v>-0.4194484100317387</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2493893903878714</v>
+        <v>-0.213439938279962</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2317236423928352</v>
+        <v>0.1059136516631209</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2331276082302339</v>
+        <v>-0.09051901621082403</v>
       </c>
       <c r="W14" t="n">
-        <v>0.106343132789043</v>
+        <v>-0.1074553156836682</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.02664494744180633</v>
+        <v>-0.05195153168821506</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.05173351856663814</v>
+        <v>-0.1585567293126599</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0552861057106372</v>
+        <v>-0.1327898705859946</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7932,55 +7932,55 @@
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.1639478249039503</v>
+        <v>0.2741125151966029</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.143058549581796</v>
+        <v>-0.09067980875359515</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.09716594459304435</v>
+        <v>0.1339516808623373</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.9943775882192768</v>
+        <v>0.620866461511249</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.169576854681374</v>
+        <v>-0.06698359757452779</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.001828018320519621</v>
+        <v>-0.1953577441296061</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
         <v>0</v>
@@ -7989,22 +7989,22 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.1403745697669546</v>
+        <v>-0.03485918139366481</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.357048098574702</v>
+        <v>-0.1025429637098657</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.4568789680399462</v>
+        <v>-0.1529163828488467</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
@@ -8019,22 +8019,22 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.1663784727276975</v>
+        <v>-0.09659529731528119</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.02609919115733312</v>
+        <v>0.03991827543658734</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.157643906313278</v>
+        <v>0.1076888653114859</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
@@ -8043,82 +8043,82 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.5297755377517586</v>
+        <v>0.4658651367002256</v>
       </c>
       <c r="BW14" t="n">
         <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1022546459280711</v>
+        <v>-0.1466441892269064</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.009162826110591533</v>
+        <v>-0.05663644740977195</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.2342812396592731</v>
+        <v>-0.2693917307771809</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.1638982556097616</v>
+        <v>0.1225584309378805</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.05737291886970274</v>
+        <v>0.03606289440584266</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.1182903537339987</v>
+        <v>-0.2738950216147675</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.1132726117835803</v>
+        <v>0.2329683320186228</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.109605938266801</v>
+        <v>0.1806825206642045</v>
       </c>
       <c r="CR14" t="n">
         <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
@@ -8127,130 +8127,130 @@
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.2059353463236435</v>
+        <v>-0.2592767152520404</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.1978817566309897</v>
+        <v>0.1318160063088256</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.04192396099197483</v>
+        <v>0.04169225927769427</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01655528575978374</v>
+        <v>0.009367822648302757</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.1319414975383897</v>
+        <v>0.01792656572225392</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.04379029078751725</v>
+        <v>-0.06991263499311016</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.1163840861417555</v>
+        <v>-0.153555039227602</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.1332675841048142</v>
+        <v>-0.05559294240138391</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.04898520635851017</v>
+        <v>-0.009211670350205219</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.06762796909316814</v>
+        <v>0.1920083883250308</v>
       </c>
       <c r="DY14" t="n">
         <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.06214252244564455</v>
+        <v>0.04516657159086612</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.08194642740223702</v>
+        <v>-0.06517409415264301</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.1881531410188559</v>
+        <v>-0.2138508613228206</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.0435897229271429</v>
+        <v>0.08334457316752628</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.04073091721653756</v>
+        <v>0.07903243057247523</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,19 +8259,19 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.05151437200643818</v>
+        <v>-0.1124680718209989</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.0995809294854095</v>
+        <v>0.1143338215331034</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02624110882317277</v>
+        <v>-0.03095076727300881</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8280,118 +8280,118 @@
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.2051242538564997</v>
+        <v>-0.2904690862704615</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.1646117835039438</v>
+        <v>0.1383886323186413</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.037123850175038</v>
+        <v>0.02208101554624424</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.1376462728594551</v>
+        <v>-0.07668614808595769</v>
       </c>
       <c r="FI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0.09741526963705273</v>
+        <v>0.09079318072854659</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.07379588356693387</v>
+        <v>-0.03634398488647607</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.01367539748003897</v>
+        <v>0.01956625424433763</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.01249638450225113</v>
+        <v>0.1024857791037667</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.03130174398166602</v>
+        <v>-0.03075049104021435</v>
       </c>
       <c r="FU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
         <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.05326290967631886</v>
+        <v>-0.2705554932739567</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.09333238338655986</v>
+        <v>0.06239421834518488</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
         <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,16 +8399,16 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4404938487472916</v>
+        <v>-0.5446253839648409</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4847887397549406</v>
+        <v>0.2413849458517419</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07246876111948647</v>
+        <v>0.09861860814464816</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8417,25 +8417,25 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3612968400823101</v>
+        <v>-0.4434104183253012</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4279789460062282</v>
+        <v>0.3117289697203432</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01623115344593665</v>
+        <v>0.1003588598589114</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8453,22 +8453,22 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1313895352390372</v>
+        <v>-0.1299243128814904</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.05168786269318988</v>
+        <v>0.06492138454683802</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.05997236158983863</v>
+        <v>-0.01217565684896109</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -8477,25 +8477,25 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1287556768363726</v>
+        <v>-0.01383304907946204</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1070815897043477</v>
+        <v>0.1235918233528284</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.07060387614115544</v>
+        <v>-0.03285439058952188</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,52 +8507,52 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.09818868120367855</v>
+        <v>-0.319812918149256</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.06047735287577899</v>
+        <v>0.08564463478932127</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.07606667321658664</v>
+        <v>-0.3256378148676898</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.2268993408059529</v>
+        <v>-0.5964552852158994</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2126391544617183</v>
+        <v>0.1446391302254315</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.008468501353027602</v>
+        <v>-0.0372896078172898</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,25 +8561,25 @@
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.167218799949917</v>
+        <v>0.08376786667061489</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1801361208885068</v>
+        <v>0.04918077410686639</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1009241754849185</v>
+        <v>0.2216355358976473</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,16 +8588,16 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.03895871490882703</v>
+        <v>0.1558584911673383</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.0002413065299595628</v>
+        <v>0.01553685073821489</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.1093972270966416</v>
+        <v>0.03169642751732146</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
@@ -8606,7 +8606,7 @@
         <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,25 +8615,25 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.09997202247263769</v>
+        <v>-0.4774291386246035</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.1141268435932596</v>
+        <v>0.1262908482495026</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.08206173515071048</v>
+        <v>-0.04856595234208742</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,103 +8642,103 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.08475702605637316</v>
+        <v>0.2900337209916085</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.1027339910991986</v>
+        <v>-0.09512018251827313</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.006745707552531694</v>
+        <v>0.01372253737765177</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.01022516873511536</v>
+        <v>0.3241239852156134</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.03292984281616092</v>
+        <v>-0.1630806568589558</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.06883031161641615</v>
+        <v>-0.1863604811862985</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.09227460586720661</v>
+        <v>0.2900269986283889</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.1008104654867707</v>
+        <v>-0.1021760069273012</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01033747257069794</v>
+        <v>3.360903626786661e-05</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1132136274548362</v>
+        <v>0.06667607249904928</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.09112495804872021</v>
+        <v>0.005519479861282042</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0001230989506506435</v>
+        <v>-0.001893770484734855</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
@@ -8747,19 +8747,19 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.03565763817709598</v>
+        <v>0.1290624718109925</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.002354929294115392</v>
+        <v>-0.00597013050286934</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.05528926815831183</v>
+        <v>0.01115412791256265</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8777,22 +8777,22 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.1076675842852843</v>
+        <v>-0.08732826075553476</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.1065165104433805</v>
+        <v>0.04187915831644291</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.07893378730664349</v>
+        <v>-0.06570894109198103</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
         <v>-0</v>
@@ -8804,25 +8804,25 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05829462809107687</v>
+        <v>0.2871792230855949</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.09431243988797126</v>
+        <v>-0.08819306375492007</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.05117308760112568</v>
+        <v>-0.04439243196041959</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
@@ -8831,25 +8831,25 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.114624404761691</v>
+        <v>0.174319114821519</v>
       </c>
       <c r="EQ15" t="n">
         <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0.06616296121463207</v>
+        <v>-0.03891260937362274</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.07439482294215694</v>
+        <v>-0.08993110835297211</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
@@ -8858,70 +8858,70 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1062930310097149</v>
+        <v>0.3264758319944808</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.09388093818488022</v>
+        <v>-0.09975196959387012</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.008375632311921634</v>
+        <v>0.01023990685528581</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.0327148609254012</v>
+        <v>0.1587548081735944</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.02840417513288346</v>
+        <v>-0.1127938068594018</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.04844501251960769</v>
+        <v>0.1160006255691364</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0152512895433851</v>
+        <v>0.03463228778808743</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.00647429024904271</v>
+        <v>0.1375446111459317</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.08648727383626534</v>
+        <v>-2.033860424401168e-05</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
@@ -8936,28 +8936,28 @@
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.04010397367413342</v>
+        <v>0.2597263430210164</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.05738228021982041</v>
+        <v>-0.03444816992035745</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
@@ -8965,46 +8965,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.3080593045172051</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>-0.1931701503029523</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5653915117213185</v>
+        <v>0.09313942533494449</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01859181874024689</v>
+        <v>-0.07820224665346835</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2689160300724986</v>
+        <v>-0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>-0.0997295878001226</v>
       </c>
       <c r="M16" t="n">
-        <v>0.542814763871265</v>
+        <v>0.06014308585533746</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07770733716657677</v>
+        <v>-0.03391307336632637</v>
       </c>
       <c r="O16" t="n">
         <v>-0</v>
@@ -9016,49 +9016,49 @@
         <v>-0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08121970910998937</v>
+        <v>-0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.05176141460591656</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1028111022777392</v>
+        <v>0.1106899235954923</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01546928266744766</v>
+        <v>0.02906255028418128</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.04423347875119706</v>
+        <v>-0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-0.02024177267011195</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0009973947678204732</v>
+        <v>-0.1220879178187778</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02192612243033993</v>
+        <v>-0.08972538095126292</v>
       </c>
       <c r="AG16" t="n">
         <v>-0</v>
@@ -9073,73 +9073,73 @@
         <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.07106363278072232</v>
+        <v>-0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>-0.09015268417082957</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.03376362690657427</v>
+        <v>0.09232215440450076</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.04846174749108102</v>
+        <v>0.01433946315911015</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
         <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.2675453854235399</v>
+        <v>-0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0.1608870001847483</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2353216096042636</v>
+        <v>0.2445330037281006</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.0632886489868966</v>
+        <v>-0.1467362320995025</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.05407322976961357</v>
+        <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0</v>
+        <v>-0.006996650466064734</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.182843626387868</v>
+        <v>-0.2062474126958554</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.1601354416634795</v>
+        <v>-0.09146386114631629</v>
       </c>
       <c r="BH16" t="n">
         <v>-0</v>
@@ -9154,19 +9154,19 @@
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.02628460580538577</v>
+        <v>-0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>0.06735484609628969</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.005751176899183403</v>
+        <v>0.0589296631575308</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.09168036981708769</v>
+        <v>0.142923860734543</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
@@ -9175,34 +9175,34 @@
         <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0.1227050701488691</v>
+        <v>-0</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0</v>
+        <v>-0.1411964760638965</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.1697653351083554</v>
+        <v>0.2924766875636164</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.09543353312632515</v>
+        <v>-0.01489025221084132</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
@@ -9211,43 +9211,43 @@
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.03583899584481814</v>
+        <v>0</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0</v>
+        <v>0.08758149427840788</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0.1037948174290201</v>
+        <v>-0.002651998444895278</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.02452058293741153</v>
+        <v>0.01722451597786693</v>
       </c>
       <c r="CI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.007682354935996818</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>0.03390504376938047</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.03759758551584347</v>
+        <v>0.0413077084824918</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.01010709895590613</v>
+        <v>0.1213622645850188</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU16" t="n">
         <v>0</v>
@@ -9265,43 +9265,43 @@
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.04751161764142826</v>
+        <v>-0</v>
       </c>
       <c r="CX16" t="n">
-        <v>0</v>
+        <v>0.0686610953472899</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0.08867664289107242</v>
+        <v>-0.0003536074070754727</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.007834071080056714</v>
+        <v>0.03028734499164009</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0814920939503672</v>
+        <v>-0</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>0.03463966349456742</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0.02836275234038218</v>
+        <v>-0.05644472232755667</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.03919735000066362</v>
+        <v>-0.01220728181982787</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,79 +9316,79 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.004647999249953114</v>
+        <v>0</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>0.0004038175159484323</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0.06740714473958247</v>
+        <v>-0.03111267650258977</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.008849231097822095</v>
+        <v>0.09339189791993321</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.050663413171135</v>
+        <v>0</v>
       </c>
       <c r="DY16" t="n">
-        <v>-0</v>
+        <v>-0.01566582199801572</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.07333936034695709</v>
+        <v>-0.00592854091951838</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.04297884511473143</v>
+        <v>-0.1332179270492126</v>
       </c>
       <c r="EB16" t="n">
         <v>-0</v>
       </c>
       <c r="EC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
         <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.003139220721396071</v>
+        <v>0</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0.03482256272183028</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0.09938119644511451</v>
+        <v>0.09634041523634716</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0009267545518877931</v>
+        <v>-0.02987596621037673</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
@@ -9400,70 +9400,70 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.09496235488426949</v>
+        <v>0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0</v>
+        <v>0.02392004604625568</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.00636364663680599</v>
+        <v>-0.0388683415346123</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.06970786213519321</v>
+        <v>-0.0213265624405962</v>
       </c>
       <c r="ET16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.05612355891363364</v>
+        <v>0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>0.07532146047081813</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.1054384514925163</v>
+        <v>-0.03051736836940876</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.009612548791270499</v>
+        <v>0.0224710711932843</v>
       </c>
       <c r="FC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01640928089850291</v>
+        <v>-0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0.1316126969586495</v>
       </c>
       <c r="FJ16" t="n">
-        <v>-0.02075985363747311</v>
+        <v>-0.06954840565519607</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.003817042154430908</v>
+        <v>-0.145865791436687</v>
       </c>
       <c r="FL16" t="n">
         <v>0</v>
@@ -9475,22 +9475,22 @@
         <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP16" t="n">
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.006598215781207548</v>
+        <v>-0</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>0.002573399715279073</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0.04584683993968883</v>
+        <v>0.0118409447235777</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.0124849849600573</v>
+        <v>0.07510217738739168</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
@@ -9499,36 +9499,1743 @@
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01279879190018728</v>
+        <v>-0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0</v>
+        <v>0.05720900325742488</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.08644856705342957</v>
+        <v>-0.06150764536814434</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
         <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.296553296321043</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.08386421679862839</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.1500721267649394</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4547444989168202</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.1716443690551115</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.1490176138912721</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.089557234850126</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1166204213792134</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.02900248203550201</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.04320654485235627</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.1904512652701777</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.02798643021238074</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.04241791619903412</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.1061515853543806</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.04629588478416746</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.5040622698555065</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.1746048808744997</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.1649127032456533</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.1041096740578058</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.07892737256568234</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.02582773867537679</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.1481820335372896</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.1273682294211523</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.04306740426012137</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0.2820694367030533</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>-0.08852684950425432</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-0.05937837820439603</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-0.09897877684306279</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.07060851666509123</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.05029519522427588</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>-0.2051653733538534</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0.1714146601847889</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0.01608842917051493</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-0.08609558826737188</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0.03436153911536925</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0.06252902384956045</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>-0.04620108329076241</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>-0.06955015256797896</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0.007671186976279003</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>-0.04403440700726632</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.02622686456185589</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0.05561164941609747</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>0.09955375976532459</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>-0.08560919799775658</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0.00305647943536508</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>-0.01329659184358909</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.02393979782069274</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0.05500268219439906</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.01068595295506298</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>-0.06462252328198528</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>0.04005488811178863</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>-0.1049829945268792</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>0.03679838445589739</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0.04795242396176172</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>-0.04707542512480138</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>0.07153489682125382</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0.01413910338087091</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0.003924079792473191</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>-0.01757207811743884</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0.05255108886387758</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>-0.09366502359791928</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>0.05613159206084595</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.4477115333607705</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4373707528134591</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2219075065312357</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.3791545992070388</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6645207800652273</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2892832714606964</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.08381182217691835</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.06366852388942988</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.02693681458922788</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.03401041912771874</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.1119154062371251</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.08958018758908165</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.2332467633192163</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.05052275587621598</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.1517782545303813</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0.503341420416805</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.08892694856433515</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.2408711624332011</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.1290255331202949</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.212270253426779</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.21021919820301</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.01352095124858344</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.08279773972430374</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.01003634625702926</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0.3293653786908884</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0.1348350037734912</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0.07628452632797306</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.1709012849205241</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-0.1487828691003954</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>-0.01856710614180537</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0.1975859340458057</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>-0.2800322882593599</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0.2386463191248788</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0.1642888597695094</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>-0.1605258664277887</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>-0.05250368769441013</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0.08873978551045228</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>-0.03672550682219589</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.01745866332147392</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0.1109709074452333</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>-0.01226051148442671</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>0.01190613042571996</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>-0.002335629785637371</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>0.1012074643914823</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>-0.04822974638491592</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>0.1511899797580462</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>-0.1596830789180162</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>-0.009302839941615825</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>0.1266589084278163</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>-0.0985548939651959</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>-0.08308972387422103</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>0.2101565618383223</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA19" t="n">
+        <v>-0.1666764884742156</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>-0.04411927477761186</v>
+      </c>
+      <c r="FC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH19" t="n">
+        <v>0.09689308715533933</v>
+      </c>
+      <c r="FI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ19" t="n">
+        <v>-0.0895791172541226</v>
+      </c>
+      <c r="FK19" t="n">
+        <v>-0.005758621922872864</v>
+      </c>
+      <c r="FL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ19" t="n">
+        <v>-0.008913386245209683</v>
+      </c>
+      <c r="FR19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS19" t="n">
+        <v>-0.03144552427103253</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>-0.004117229413038137</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ19" t="n">
+        <v>0.150605215687692</v>
+      </c>
+      <c r="GA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB19" t="n">
+        <v>-0.05598005398596194</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG19" t="n">
         <v>0</v>
       </c>
     </row>
